--- a/记录人生/ゼノブレイド２攻略.xlsx
+++ b/记录人生/ゼノブレイド２攻略.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="300">
   <si>
     <t>编号</t>
   </si>
@@ -103,6 +103,9 @@
     <t>クーマラヴァ店権利書</t>
   </si>
   <si>
+    <t>已取得</t>
+  </si>
+  <si>
     <t>グリラフ店権利書</t>
   </si>
   <si>
@@ -139,9 +142,6 @@
     <t>ペルーニ店権利書</t>
   </si>
   <si>
-    <t>已取得</t>
-  </si>
-  <si>
     <t>英维迪亚</t>
   </si>
   <si>
@@ -229,6 +229,9 @@
     <t>プルミエ店権利書</t>
   </si>
   <si>
+    <t>获得心相点数时额外 +1</t>
+  </si>
+  <si>
     <t>ライネン店権利書</t>
   </si>
   <si>
@@ -382,6 +385,9 @@
     <t>新たなる力</t>
   </si>
   <si>
+    <t>已完成</t>
+  </si>
+  <si>
     <t>アザミ</t>
   </si>
   <si>
@@ -557,9 +563,6 @@
   </si>
   <si>
     <t>第一話以降</t>
-  </si>
-  <si>
-    <t>已完成</t>
   </si>
   <si>
     <t>積荷の護衛</t>
@@ -959,7 +962,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -991,7 +994,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1497,10 +1500,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3">
@@ -1632,7 +1635,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1912,6 +1915,18 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DeedsTable" displayName="DeedsTable" ref="A1:E53">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E53" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="斯佩比亚"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="未确认"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="5">
     <tableColumn id="1" name="编号" dataDxfId="0"/>
     <tableColumn id="2" name="地区(中文)" dataDxfId="1"/>
@@ -1941,9 +1956,9 @@
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A2:E113" totalsRowShown="0">
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E113" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="4">
+    <filterColumn colId="1">
       <filters>
-        <filter val="进行中"/>
+        <filter val="アーケディア"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2235,7 +2250,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:5">
+    <row r="2" ht="16.5" hidden="1" spans="1:5">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -2252,7 +2267,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:5">
+    <row r="3" ht="16.5" hidden="1" spans="1:5">
       <c r="A3" s="12">
         <v>2</v>
       </c>
@@ -2269,7 +2284,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="16.5" spans="1:5">
+    <row r="4" ht="16.5" hidden="1" spans="1:5">
       <c r="A4" s="12">
         <v>3</v>
       </c>
@@ -2286,7 +2301,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:5">
+    <row r="5" ht="16.5" hidden="1" spans="1:5">
       <c r="A5" s="12">
         <v>4</v>
       </c>
@@ -2303,7 +2318,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:5">
+    <row r="6" ht="16.5" hidden="1" spans="1:5">
       <c r="A6" s="12">
         <v>5</v>
       </c>
@@ -2320,7 +2335,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:5">
+    <row r="7" ht="16.5" hidden="1" spans="1:5">
       <c r="A7" s="12">
         <v>6</v>
       </c>
@@ -2337,7 +2352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:5">
+    <row r="8" ht="16.5" hidden="1" spans="1:5">
       <c r="A8" s="12">
         <v>7</v>
       </c>
@@ -2354,7 +2369,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:5">
+    <row r="9" ht="16.5" hidden="1" spans="1:5">
       <c r="A9" s="12">
         <v>8</v>
       </c>
@@ -2371,7 +2386,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:5">
+    <row r="10" ht="16.5" hidden="1" spans="1:5">
       <c r="A10" s="12">
         <v>9</v>
       </c>
@@ -2385,10 +2400,10 @@
         <v>14</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" hidden="1" spans="1:5">
       <c r="A11" s="12">
         <v>10</v>
       </c>
@@ -2396,16 +2411,16 @@
         <v>22</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" ht="16.5" spans="1:5">
+    <row r="12" ht="16.5" hidden="1" spans="1:5">
       <c r="A12" s="12">
         <v>11</v>
       </c>
@@ -2413,16 +2428,16 @@
         <v>22</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" hidden="1" spans="1:5">
       <c r="A13" s="12">
         <v>12</v>
       </c>
@@ -2430,7 +2445,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>20</v>
@@ -2439,7 +2454,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" ht="16.5" spans="1:5">
+    <row r="14" ht="16.5" hidden="1" spans="1:5">
       <c r="A14" s="12">
         <v>13</v>
       </c>
@@ -2447,16 +2462,16 @@
         <v>22</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" hidden="1" spans="1:5">
       <c r="A15" s="12">
         <v>14</v>
       </c>
@@ -2464,16 +2479,16 @@
         <v>22</v>
       </c>
       <c r="C15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>30</v>
-      </c>
       <c r="E15" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" ht="16.5" spans="1:5">
+    <row r="16" ht="16.5" hidden="1" spans="1:5">
       <c r="A16" s="12">
         <v>15</v>
       </c>
@@ -2481,16 +2496,16 @@
         <v>22</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>7</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" hidden="1" spans="1:5">
       <c r="A17" s="12">
         <v>16</v>
       </c>
@@ -2498,16 +2513,16 @@
         <v>22</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" ht="16.5" spans="1:5">
+    <row r="18" ht="16.5" hidden="1" spans="1:5">
       <c r="A18" s="12">
         <v>17</v>
       </c>
@@ -2515,16 +2530,16 @@
         <v>22</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>7</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" hidden="1" spans="1:5">
       <c r="A19" s="12">
         <v>18</v>
       </c>
@@ -2541,7 +2556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" ht="16.5" spans="1:5">
+    <row r="20" ht="16.5" hidden="1" spans="1:5">
       <c r="A20" s="12">
         <v>19</v>
       </c>
@@ -2552,13 +2567,13 @@
         <v>40</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" ht="16.5" spans="1:5">
+    <row r="21" ht="16.5" hidden="1" spans="1:5">
       <c r="A21" s="12">
         <v>20</v>
       </c>
@@ -2569,13 +2584,13 @@
         <v>41</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" ht="16.5" spans="1:5">
+    <row r="22" ht="16.5" hidden="1" spans="1:5">
       <c r="A22" s="12">
         <v>21</v>
       </c>
@@ -2589,10 +2604,10 @@
         <v>10</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" hidden="1" spans="1:5">
       <c r="A23" s="12">
         <v>22</v>
       </c>
@@ -2603,13 +2618,13 @@
         <v>43</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" hidden="1" spans="1:5">
       <c r="A24" s="12">
         <v>23</v>
       </c>
@@ -2626,7 +2641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" ht="16.5" spans="1:5">
+    <row r="25" ht="16.5" hidden="1" spans="1:5">
       <c r="A25" s="12">
         <v>24</v>
       </c>
@@ -2637,13 +2652,13 @@
         <v>45</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="26" ht="16.5" spans="1:5">
+    <row r="26" ht="16.5" hidden="1" spans="1:5">
       <c r="A26" s="12">
         <v>25</v>
       </c>
@@ -2660,7 +2675,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" ht="16.5" spans="1:5">
+    <row r="27" ht="16.5" hidden="1" spans="1:5">
       <c r="A27" s="12">
         <v>26</v>
       </c>
@@ -2671,13 +2686,13 @@
         <v>47</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" ht="16.5" spans="1:5">
+    <row r="28" ht="16.5" hidden="1" spans="1:5">
       <c r="A28" s="12">
         <v>27</v>
       </c>
@@ -2688,13 +2703,13 @@
         <v>48</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" hidden="1" spans="1:5">
       <c r="A29" s="12">
         <v>28</v>
       </c>
@@ -2711,7 +2726,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" ht="16.5" spans="1:5">
+    <row r="30" ht="16.5" hidden="1" spans="1:5">
       <c r="A30" s="12">
         <v>29</v>
       </c>
@@ -2722,7 +2737,7 @@
         <v>50</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>8</v>
@@ -2790,7 +2805,7 @@
         <v>55</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>8</v>
@@ -2810,10 +2825,10 @@
         <v>39</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" hidden="1" spans="1:5">
       <c r="A36" s="12">
         <v>35</v>
       </c>
@@ -2827,7 +2842,7 @@
         <v>58</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:5">
@@ -2858,13 +2873,13 @@
         <v>60</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="39" ht="16.5" spans="1:5">
+    <row r="39" ht="16.5" hidden="1" spans="1:5">
       <c r="A39" s="12">
         <v>38</v>
       </c>
@@ -2875,13 +2890,13 @@
         <v>62</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="40" ht="16.5" spans="1:5">
+    <row r="40" ht="16.5" hidden="1" spans="1:5">
       <c r="A40" s="12">
         <v>39</v>
       </c>
@@ -2892,13 +2907,13 @@
         <v>63</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="41" ht="16.5" spans="1:5">
+    <row r="41" ht="16.5" hidden="1" spans="1:5">
       <c r="A41" s="12">
         <v>40</v>
       </c>
@@ -2915,7 +2930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" ht="16.5" spans="1:5">
+    <row r="42" ht="16.5" hidden="1" spans="1:5">
       <c r="A42" s="12">
         <v>41</v>
       </c>
@@ -2926,13 +2941,13 @@
         <v>65</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" ht="16.5" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" hidden="1" spans="1:5">
       <c r="A43" s="12">
         <v>42</v>
       </c>
@@ -2940,16 +2955,16 @@
         <v>61</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" ht="16.5" spans="1:5">
+    <row r="44" ht="16.5" hidden="1" spans="1:5">
       <c r="A44" s="12">
         <v>43</v>
       </c>
@@ -2957,7 +2972,7 @@
         <v>61</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D44" s="12" t="s">
         <v>10</v>
@@ -2966,15 +2981,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" ht="16.5" spans="1:5">
+    <row r="45" ht="16.5" hidden="1" spans="1:5">
       <c r="A45" s="12">
         <v>44</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D45" s="12" t="s">
         <v>20</v>
@@ -2983,15 +2998,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" ht="16.5" spans="1:5">
+    <row r="46" ht="16.5" hidden="1" spans="1:5">
       <c r="A46" s="12">
         <v>45</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D46" s="12" t="s">
         <v>14</v>
@@ -3000,32 +3015,32 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" ht="16.5" spans="1:5">
+    <row r="47" ht="16.5" hidden="1" spans="1:5">
       <c r="A47" s="12">
         <v>46</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="48" ht="16.5" spans="1:5">
+    <row r="48" ht="16.5" hidden="1" spans="1:5">
       <c r="A48" s="12">
         <v>47</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D48" s="12" t="s">
         <v>12</v>
@@ -3034,15 +3049,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" ht="16.5" spans="1:5">
+    <row r="49" ht="16.5" hidden="1" spans="1:5">
       <c r="A49" s="12">
         <v>48</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>12</v>
@@ -3051,32 +3066,32 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" ht="16.5" spans="1:5">
+    <row r="50" ht="16.5" hidden="1" spans="1:5">
       <c r="A50" s="12">
         <v>49</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="51" ht="16.5" spans="1:5">
+    <row r="51" ht="16.5" hidden="1" spans="1:5">
       <c r="A51" s="12">
         <v>50</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>20</v>
@@ -3085,15 +3100,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" ht="16.5" spans="1:5">
+    <row r="52" ht="16.5" hidden="1" spans="1:5">
       <c r="A52" s="12">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D52" s="12" t="s">
         <v>10</v>
@@ -3102,15 +3117,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" ht="16.5" spans="1:5">
+    <row r="53" ht="16.5" hidden="1" spans="1:5">
       <c r="A53" s="12">
         <v>52</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D53" s="12" t="s">
         <v>20</v>
@@ -3161,7 +3176,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3169,19 +3184,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>4</v>
@@ -3192,19 +3207,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>8</v>
@@ -3215,19 +3230,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>89</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>8</v>
@@ -3238,19 +3253,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>8</v>
@@ -3261,19 +3276,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>8</v>
@@ -3284,19 +3299,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>8</v>
@@ -3307,19 +3322,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>8</v>
@@ -3330,22 +3345,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:7">
@@ -3353,19 +3368,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>8</v>
@@ -3376,19 +3391,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>8</v>
@@ -3399,19 +3414,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>8</v>
@@ -3422,19 +3437,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>8</v>
@@ -3445,22 +3460,22 @@
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>113</v>
-      </c>
       <c r="G14" s="7" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
@@ -3468,19 +3483,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>8</v>
@@ -3491,19 +3506,19 @@
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>118</v>
-      </c>
       <c r="E16" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>8</v>
@@ -3514,19 +3529,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>8</v>
@@ -3537,19 +3552,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>8</v>
@@ -3560,19 +3575,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>8</v>
@@ -3583,19 +3598,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G20" s="7" t="s">
         <v>8</v>
@@ -3606,19 +3621,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>8</v>
@@ -3629,19 +3644,19 @@
         <v>20</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>8</v>
@@ -3652,19 +3667,19 @@
         <v>21</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>8</v>
@@ -3675,19 +3690,19 @@
         <v>22</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>137</v>
-      </c>
       <c r="E24" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>8</v>
@@ -3698,19 +3713,19 @@
         <v>23</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>8</v>
@@ -3721,19 +3736,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>8</v>
@@ -3744,19 +3759,19 @@
         <v>25</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C27" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>144</v>
-      </c>
       <c r="E27" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>8</v>
@@ -3767,19 +3782,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>8</v>
@@ -3790,19 +3805,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>8</v>
@@ -3813,19 +3828,19 @@
         <v>28</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C30" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="D30" s="10" t="s">
-        <v>152</v>
-      </c>
       <c r="E30" s="10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>8</v>
@@ -3836,19 +3851,19 @@
         <v>29</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>8</v>
@@ -3859,19 +3874,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>8</v>
@@ -3882,19 +3897,19 @@
         <v>31</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>8</v>
@@ -3905,19 +3920,19 @@
         <v>32</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>8</v>
@@ -3928,19 +3943,19 @@
         <v>33</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>8</v>
@@ -3951,19 +3966,19 @@
         <v>34</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>8</v>
@@ -4010,7 +4025,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:5">
@@ -4018,13 +4033,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>4</v>
@@ -4035,16 +4050,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" ht="16.5" hidden="1" spans="1:5">
@@ -4052,16 +4067,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>175</v>
-      </c>
       <c r="E4" s="7" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" ht="16.5" hidden="1" spans="1:5">
@@ -4069,50 +4084,50 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" hidden="1" spans="1:5">
       <c r="A6" s="6">
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" hidden="1" spans="1:5">
       <c r="A7" s="4">
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" ht="16.5" hidden="1" spans="1:5">
@@ -4120,16 +4135,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" ht="16.5" hidden="1" spans="1:5">
@@ -4137,13 +4152,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>8</v>
@@ -4154,13 +4169,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>8</v>
@@ -4171,13 +4186,13 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>184</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>8</v>
@@ -4188,13 +4203,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>8</v>
@@ -4205,13 +4220,13 @@
         <v>11</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>187</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>8</v>
@@ -4222,16 +4237,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" ht="16.5" hidden="1" spans="1:5">
@@ -4239,16 +4254,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>190</v>
-      </c>
       <c r="E15" s="7" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" ht="16.5" hidden="1" spans="1:5">
@@ -4256,16 +4271,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" ht="16.5" hidden="1" spans="1:5">
@@ -4273,16 +4288,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" ht="16.5" hidden="1" spans="1:5">
@@ -4290,16 +4305,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>194</v>
-      </c>
       <c r="E18" s="5" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" ht="16.5" hidden="1" spans="1:5">
@@ -4307,16 +4322,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" ht="16.5" hidden="1" spans="1:5">
@@ -4324,16 +4339,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" ht="16.5" hidden="1" spans="1:5">
@@ -4341,16 +4356,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" ht="16.5" hidden="1" spans="1:5">
@@ -4358,16 +4373,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" ht="16.5" hidden="1" spans="1:5">
@@ -4375,16 +4390,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" ht="16.5" hidden="1" spans="1:5">
@@ -4392,33 +4407,33 @@
         <v>22</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" hidden="1" spans="1:5">
       <c r="A25" s="4">
         <v>23</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" ht="16.5" hidden="1" spans="1:5">
@@ -4426,13 +4441,13 @@
         <v>24</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>8</v>
@@ -4443,13 +4458,13 @@
         <v>25</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>8</v>
@@ -4460,13 +4475,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>8</v>
@@ -4477,13 +4492,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>8</v>
@@ -4494,16 +4509,16 @@
         <v>28</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" ht="16.5" hidden="1" spans="1:5">
@@ -4511,16 +4526,16 @@
         <v>29</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" ht="16.5" hidden="1" spans="1:5">
@@ -4528,13 +4543,13 @@
         <v>30</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>8</v>
@@ -4545,13 +4560,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>8</v>
@@ -4562,13 +4577,13 @@
         <v>32</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>8</v>
@@ -4579,13 +4594,13 @@
         <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>8</v>
@@ -4596,13 +4611,13 @@
         <v>34</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>8</v>
@@ -4613,13 +4628,13 @@
         <v>35</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>8</v>
@@ -4630,13 +4645,13 @@
         <v>36</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>8</v>
@@ -4647,13 +4662,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>8</v>
@@ -4664,16 +4679,16 @@
         <v>38</v>
       </c>
       <c r="B40" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E40" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="41" ht="16.5" hidden="1" spans="1:5">
@@ -4681,16 +4696,16 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="42" ht="16.5" hidden="1" spans="1:5">
@@ -4698,16 +4713,16 @@
         <v>40</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="43" ht="16.5" hidden="1" spans="1:5">
@@ -4715,33 +4730,33 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E43" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="44" ht="16.5" spans="1:5">
+    </row>
+    <row r="44" ht="16.5" hidden="1" spans="1:5">
       <c r="A44" s="6">
         <v>42</v>
       </c>
       <c r="B44" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E44" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="45" ht="16.5" hidden="1" spans="1:5">
@@ -4749,16 +4764,16 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" ht="16.5" hidden="1" spans="1:5">
@@ -4766,13 +4781,13 @@
         <v>44</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>8</v>
@@ -4783,13 +4798,13 @@
         <v>45</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>8</v>
@@ -4800,33 +4815,33 @@
         <v>46</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="49" ht="16.5" spans="1:5">
+    <row r="49" ht="16.5" hidden="1" spans="1:5">
       <c r="A49" s="4">
         <v>47</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="50" ht="16.5" hidden="1" spans="1:5">
@@ -4834,13 +4849,13 @@
         <v>48</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C50" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>229</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>228</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>8</v>
@@ -4851,13 +4866,13 @@
         <v>49</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>8</v>
@@ -4868,13 +4883,13 @@
         <v>50</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>8</v>
@@ -4885,13 +4900,13 @@
         <v>51</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>8</v>
@@ -4902,13 +4917,13 @@
         <v>52</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>8</v>
@@ -4919,13 +4934,13 @@
         <v>53</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>8</v>
@@ -4936,13 +4951,13 @@
         <v>54</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>8</v>
@@ -4953,13 +4968,13 @@
         <v>55</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>8</v>
@@ -4970,16 +4985,16 @@
         <v>56</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" ht="16.5" hidden="1" spans="1:5">
@@ -4987,50 +5002,50 @@
         <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="60" ht="16.5" spans="1:5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" hidden="1" spans="1:5">
       <c r="A60" s="6">
         <v>58</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="61" ht="16.5" spans="1:5">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" hidden="1" spans="1:5">
       <c r="A61" s="4">
         <v>59</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" ht="16.5" hidden="1" spans="1:5">
@@ -5038,16 +5053,16 @@
         <v>60</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C62" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="D62" s="7" t="s">
-        <v>241</v>
-      </c>
       <c r="E62" s="7" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" ht="16.5" hidden="1" spans="1:5">
@@ -5055,13 +5070,13 @@
         <v>61</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>8</v>
@@ -5072,13 +5087,13 @@
         <v>62</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>8</v>
@@ -5089,13 +5104,13 @@
         <v>63</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>8</v>
@@ -5106,13 +5121,13 @@
         <v>64</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>8</v>
@@ -5123,13 +5138,13 @@
         <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>8</v>
@@ -5140,13 +5155,13 @@
         <v>66</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>8</v>
@@ -5157,13 +5172,13 @@
         <v>67</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>8</v>
@@ -5174,13 +5189,13 @@
         <v>68</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>8</v>
@@ -5191,13 +5206,13 @@
         <v>69</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>8</v>
@@ -5208,13 +5223,13 @@
         <v>70</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>8</v>
@@ -5225,13 +5240,13 @@
         <v>71</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>8</v>
@@ -5242,13 +5257,13 @@
         <v>72</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>8</v>
@@ -5259,13 +5274,13 @@
         <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>8</v>
@@ -5276,13 +5291,13 @@
         <v>74</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C76" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D76" s="7" t="s">
         <v>256</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>255</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>8</v>
@@ -5293,64 +5308,64 @@
         <v>75</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="78" ht="16.5" hidden="1" spans="1:5">
+    <row r="78" ht="16.5" spans="1:5">
       <c r="A78" s="6">
         <v>76</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" ht="16.5" hidden="1" spans="1:5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:5">
       <c r="A79" s="4">
         <v>77</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" ht="16.5" hidden="1" spans="1:5">
+        <v>114</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:5">
       <c r="A80" s="6">
         <v>78</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>8</v>
@@ -5361,13 +5376,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>8</v>
@@ -5378,13 +5393,13 @@
         <v>80</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>8</v>
@@ -5395,13 +5410,13 @@
         <v>81</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>8</v>
@@ -5412,13 +5427,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E84" s="7" t="s">
         <v>8</v>
@@ -5429,13 +5444,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>8</v>
@@ -5446,13 +5461,13 @@
         <v>84</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>8</v>
@@ -5463,13 +5478,13 @@
         <v>85</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>8</v>
@@ -5480,13 +5495,13 @@
         <v>86</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>8</v>
@@ -5497,13 +5512,13 @@
         <v>87</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E89" s="5" t="s">
         <v>8</v>
@@ -5514,13 +5529,13 @@
         <v>88</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>8</v>
@@ -5531,16 +5546,16 @@
         <v>89</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92" ht="16.5" hidden="1" spans="1:5">
@@ -5548,16 +5563,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E92" s="8" t="s">
         <v>118</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="93" ht="16.5" hidden="1" spans="1:5">
@@ -5565,13 +5580,13 @@
         <v>91</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E93" s="8" t="s">
         <v>8</v>
@@ -5582,13 +5597,13 @@
         <v>92</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E94" s="8" t="s">
         <v>8</v>
@@ -5599,33 +5614,33 @@
         <v>93</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="96" ht="16.5" spans="1:5">
+    <row r="96" ht="16.5" hidden="1" spans="1:5">
       <c r="A96" s="6">
         <v>94</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="97" ht="16.5" hidden="1" spans="1:5">
@@ -5633,13 +5648,13 @@
         <v>95</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E97" s="8" t="s">
         <v>8</v>
@@ -5650,13 +5665,13 @@
         <v>96</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E98" s="8" t="s">
         <v>8</v>
@@ -5667,13 +5682,13 @@
         <v>97</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E99" s="8" t="s">
         <v>8</v>
@@ -5684,13 +5699,13 @@
         <v>98</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E100" s="8" t="s">
         <v>8</v>
@@ -5701,16 +5716,16 @@
         <v>99</v>
       </c>
       <c r="B101" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E101" s="8" t="s">
         <v>118</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="D101" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="102" ht="16.5" hidden="1" spans="1:5">
@@ -5718,16 +5733,16 @@
         <v>100</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" ht="16.5" hidden="1" spans="1:5">
@@ -5735,13 +5750,13 @@
         <v>101</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E103" s="8" t="s">
         <v>8</v>
@@ -5752,13 +5767,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E104" s="8" t="s">
         <v>8</v>
@@ -5769,13 +5784,13 @@
         <v>103</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>8</v>
@@ -5786,16 +5801,16 @@
         <v>104</v>
       </c>
       <c r="B106" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E106" s="8" t="s">
         <v>118</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="D106" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="107" ht="16.5" hidden="1" spans="1:5">
@@ -5803,13 +5818,13 @@
         <v>105</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E107" s="8" t="s">
         <v>8</v>
@@ -5820,13 +5835,13 @@
         <v>106</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E108" s="8" t="s">
         <v>8</v>
@@ -5837,13 +5852,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E109" s="8" t="s">
         <v>8</v>
@@ -5854,13 +5869,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E110" s="8" t="s">
         <v>8</v>
@@ -5871,13 +5886,13 @@
         <v>109</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C111" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D111" s="8" t="s">
         <v>296</v>
-      </c>
-      <c r="D111" s="8" t="s">
-        <v>295</v>
       </c>
       <c r="E111" s="8" t="s">
         <v>8</v>
@@ -5888,13 +5903,13 @@
         <v>110</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E112" s="8" t="s">
         <v>8</v>
@@ -5905,13 +5920,13 @@
         <v>111</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E113" s="8" t="s">
         <v>8</v>
@@ -5944,7 +5959,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E3 E14 E17 E20 E58 E59 E4:E5 E6:E13 E15:E16 E18:E19 E21:E22 E23:E41 E42:E43 E44:E57 E60:E61 E62:E90 E91:E113">
+    <dataValidation type="list" sqref="E3 E14 E17 E20 E58 E59 E60 E4:E5 E6:E13 E15:E16 E18:E19 E21:E22 E23:E41 E42:E43 E44:E57 E61:E62 E63:E77 E78:E79 E80:E90 E91:E113">
       <formula1>"未确认,未完成,进行中,已完成,暂不做"</formula1>
     </dataValidation>
   </dataValidations>

--- a/记录人生/ゼノブレイド２攻略.xlsx
+++ b/记录人生/ゼノブレイド２攻略.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25590" windowHeight="12800" activeTab="2"/>
+    <workbookView windowWidth="25590" windowHeight="12800"/>
   </bookViews>
   <sheets>
     <sheet name="产权证" sheetId="1" r:id="rId1"/>
@@ -79,33 +79,36 @@
     <t>ハナマル店権利書</t>
   </si>
   <si>
+    <t>获得心相点数时额外 +1</t>
+  </si>
+  <si>
+    <t>已取得</t>
+  </si>
+  <si>
+    <t>ハニーシロップ店権利書</t>
+  </si>
+  <si>
+    <t>获得发展点数时额外 +1</t>
+  </si>
+  <si>
+    <t>ハラペッコ店権利書</t>
+  </si>
+  <si>
+    <t>战斗经验值 +10%</t>
+  </si>
+  <si>
+    <t>ピッチピッチ店権利書</t>
+  </si>
+  <si>
     <t>获得理念点数时额外 +1</t>
   </si>
   <si>
-    <t>ハニーシロップ店権利書</t>
-  </si>
-  <si>
-    <t>获得发展点数时额外 +1</t>
-  </si>
-  <si>
-    <t>ハラペッコ店権利書</t>
-  </si>
-  <si>
-    <t>战斗经验值 +10%</t>
-  </si>
-  <si>
-    <t>ピッチピッチ店権利書</t>
-  </si>
-  <si>
     <t>古拉</t>
   </si>
   <si>
     <t>クーマラヴァ店権利書</t>
   </si>
   <si>
-    <t>已取得</t>
-  </si>
-  <si>
     <t>グリラフ店権利書</t>
   </si>
   <si>
@@ -229,9 +232,6 @@
     <t>プルミエ店権利書</t>
   </si>
   <si>
-    <t>获得心相点数时额外 +1</t>
-  </si>
-  <si>
     <t>ライネン店権利書</t>
   </si>
   <si>
@@ -581,6 +581,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>バーンの隠し財産</t>
     </r>
     <r>
@@ -1863,35 +1868,30 @@
         <name val="微软雅黑"/>
         <scheme val="none"/>
       </font>
-      <alignment/>
     </dxf>
     <dxf>
       <font>
         <name val="微软雅黑"/>
         <scheme val="none"/>
       </font>
-      <alignment/>
     </dxf>
     <dxf>
       <font>
         <name val="微软雅黑"/>
         <scheme val="none"/>
       </font>
-      <alignment/>
     </dxf>
     <dxf>
       <font>
         <name val="微软雅黑"/>
         <scheme val="none"/>
       </font>
-      <alignment/>
     </dxf>
     <dxf>
       <font>
         <name val="微软雅黑"/>
         <scheme val="none"/>
       </font>
-      <alignment/>
     </dxf>
     <dxf>
       <font>
@@ -1916,14 +1916,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DeedsTable" displayName="DeedsTable" ref="A1:E53">
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E53" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
+    <filterColumn colId="3">
       <filters>
-        <filter val="斯佩比亚"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="未确认"/>
+        <filter val="掉落道具收集距离 +50cm"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -1958,7 +1953,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E113" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="1">
       <filters>
-        <filter val="アーケディア"/>
+        <filter val="テンペランティア"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2250,7 +2245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="16.5" hidden="1" spans="1:5">
+    <row r="2" ht="16.5" spans="1:5">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -2332,7 +2327,7 @@
         <v>16</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" ht="16.5" hidden="1" spans="1:5">
@@ -2343,13 +2338,13 @@
         <v>5</v>
       </c>
       <c r="C7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="8" ht="16.5" hidden="1" spans="1:5">
@@ -2360,10 +2355,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>8</v>
@@ -2377,10 +2372,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>8</v>
@@ -2391,16 +2386,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" ht="16.5" hidden="1" spans="1:5">
@@ -2408,13 +2403,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>8</v>
@@ -2425,16 +2420,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" ht="16.5" hidden="1" spans="1:5">
@@ -2442,13 +2437,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>8</v>
@@ -2459,16 +2454,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="16.5" hidden="1" spans="1:5">
@@ -2476,33 +2471,33 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>31</v>
-      </c>
       <c r="E15" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" ht="16.5" hidden="1" spans="1:5">
+    <row r="16" ht="16.5" spans="1:5">
       <c r="A16" s="12">
         <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>7</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" ht="16.5" hidden="1" spans="1:5">
@@ -2510,33 +2505,33 @@
         <v>16</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" ht="16.5" hidden="1" spans="1:5">
+    <row r="18" ht="16.5" spans="1:5">
       <c r="A18" s="12">
         <v>17</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>7</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" ht="16.5" hidden="1" spans="1:5">
@@ -2544,13 +2539,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>8</v>
@@ -2561,13 +2556,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>8</v>
@@ -2578,13 +2573,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>8</v>
@@ -2595,16 +2590,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" ht="16.5" hidden="1" spans="1:5">
@@ -2612,27 +2607,27 @@
         <v>22</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" hidden="1" spans="1:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="12">
         <v>23</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>7</v>
@@ -2646,13 +2641,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>8</v>
@@ -2663,13 +2658,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>8</v>
@@ -2680,13 +2675,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>8</v>
@@ -2697,16 +2692,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" ht="16.5" hidden="1" spans="1:5">
@@ -2714,10 +2709,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>14</v>
@@ -2731,13 +2726,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>8</v>
@@ -2748,44 +2743,44 @@
         <v>30</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D31" s="12" t="s">
         <v>7</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" hidden="1" spans="1:5">
       <c r="A32" s="12">
         <v>31</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>10</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" spans="1:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" hidden="1" spans="1:5">
       <c r="A33" s="12">
         <v>32</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D33" s="12" t="s">
         <v>14</v>
@@ -2794,38 +2789,38 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" ht="16.5" spans="1:5">
+    <row r="34" ht="16.5" hidden="1" spans="1:5">
       <c r="A34" s="12">
         <v>33</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" spans="1:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" hidden="1" spans="1:5">
       <c r="A35" s="12">
         <v>34</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36" ht="16.5" hidden="1" spans="1:5">
@@ -2833,47 +2828,47 @@
         <v>35</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" ht="16.5" spans="1:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" hidden="1" spans="1:5">
       <c r="A37" s="12">
         <v>36</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C37" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D37" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D37" s="12" t="s">
-        <v>58</v>
-      </c>
       <c r="E37" s="12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" ht="16.5" spans="1:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" hidden="1" spans="1:5">
       <c r="A38" s="12">
         <v>37</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>8</v>
@@ -2884,13 +2879,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>8</v>
@@ -2901,13 +2896,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>8</v>
@@ -2918,13 +2913,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E41" s="12" t="s">
         <v>8</v>
@@ -2935,16 +2930,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" ht="16.5" hidden="1" spans="1:5">
@@ -2952,13 +2947,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>67</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>8</v>
@@ -2969,7 +2964,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>68</v>
@@ -2992,7 +2987,7 @@
         <v>70</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>8</v>
@@ -3026,7 +3021,7 @@
         <v>72</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>8</v>
@@ -3077,7 +3072,7 @@
         <v>75</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>8</v>
@@ -3094,7 +3089,7 @@
         <v>76</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>8</v>
@@ -3128,7 +3123,7 @@
         <v>78</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>8</v>
@@ -4858,7 +4853,7 @@
         <v>229</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" ht="16.5" hidden="1" spans="1:5">
@@ -5028,7 +5023,7 @@
         <v>104</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" ht="16.5" hidden="1" spans="1:5">
@@ -5320,7 +5315,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" ht="16.5" spans="1:5">
+    <row r="78" ht="16.5" hidden="1" spans="1:5">
       <c r="A78" s="6">
         <v>76</v>
       </c>
@@ -5337,7 +5332,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="79" ht="16.5" spans="1:5">
+    <row r="79" ht="16.5" hidden="1" spans="1:5">
       <c r="A79" s="4">
         <v>77</v>
       </c>
@@ -5354,7 +5349,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="80" ht="16.5" spans="1:5">
+    <row r="80" ht="16.5" hidden="1" spans="1:5">
       <c r="A80" s="6">
         <v>78</v>
       </c>
@@ -5368,10 +5363,10 @@
         <v>211</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" ht="16.5" hidden="1" spans="1:5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" spans="1:5">
       <c r="A81" s="4">
         <v>79</v>
       </c>
@@ -5385,7 +5380,7 @@
         <v>211</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
     </row>
     <row r="82" ht="16.5" hidden="1" spans="1:5">
@@ -5959,7 +5954,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E3 E14 E17 E20 E58 E59 E60 E4:E5 E6:E13 E15:E16 E18:E19 E21:E22 E23:E41 E42:E43 E44:E57 E61:E62 E63:E77 E78:E79 E80:E90 E91:E113">
+    <dataValidation type="list" sqref="E3:E113">
       <formula1>"未确认,未完成,进行中,已完成,暂不做"</formula1>
     </dataValidation>
   </dataValidations>
